--- a/base/pacotes/arthen-arboris/parametrico-arthen-arboris.xlsx
+++ b/base/pacotes/arthen-arboris/parametrico-arthen-arboris.xlsx
@@ -97,7 +97,7 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00E74C3C"/>
+      <color rgb="00E67E22"/>
       <sz val="9"/>
     </font>
     <font>
@@ -106,8 +106,9 @@
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="00999999"/>
-      <sz val="8"/>
+      <b val="1"/>
+      <color rgb="0027AE60"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -184,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -204,7 +205,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -593,7 +595,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PROJETO — PARAMÉTRICO V2</t>
+          <t>ARTHEN ARBORIS — PARAMÉTRICO V2</t>
         </is>
       </c>
     </row>
@@ -758,14 +760,14 @@
           <t>ALVENARIA</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F9</f>
         <v/>
       </c>
@@ -808,177 +810,177 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Bloco cerâm.</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Vedação 14cm</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B13*DADOS_PROJETO!B5*0.40,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D13*DADOS_PROJETO!B5*0.40,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>32.95</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ 2,25×40%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Drywall ST</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Internas</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B13*DADOS_PROJETO!B5*0.25,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D13*DADOS_PROJETO!B5*0.25,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>156</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Índ 2,25×25%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Drywall RU</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Molhadas</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B13*DADOS_PROJETO!B5*0.08,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D13*DADOS_PROJETO!B5*0.08,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>195</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Índ 2,25×8%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Argamassa</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Assentamento</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B13*DADOS_PROJETO!B5*0.40,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D13*DADOS_PROJETO!B5*0.40,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>3.8</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>MO Alvenaria</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(INDICES!B13*DADOS_PROJETO!B5*0.40,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D13*DADOS_PROJETO!B5*0.40,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>28.5</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Split 35,7% (9p)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <f>SUM(F4:F8)</f>
         <v/>
       </c>
@@ -1016,14 +1018,14 @@
           <t>IMPERMEABILIZAÇÃO</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F9</f>
         <v/>
       </c>
@@ -1066,177 +1068,177 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Manta 4mm</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B19*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D19*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>82.11</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ impermeab×AC</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Arg.polim.</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>BWC</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B19*DADOS_PROJETO!B5*0.3,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D19*DADOS_PROJETO!B5*0.3,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>8.5</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Regulariz.</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Superfície</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B19*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D19*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>5.57</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>PU base (15p)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>MO imper.</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B19*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D19*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>68</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>Split 56,5% (6p)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>MO regul.</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(INDICES!B19*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D19*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>19.5</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>PU base (7p)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="22">
         <f>SUM(F4:F8)</f>
         <v/>
       </c>
@@ -1274,14 +1276,14 @@
           <t>INSTALAÇÕES</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F11</f>
         <v/>
       </c>
@@ -1324,12 +1326,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Elétricas mat.</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>IF Tipologia</t>
         </is>
@@ -1338,32 +1340,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E4" s="5">
-        <f>ROUND(130*(DADOS_PROJETO!B12/2752.67)/1.1*0.618*INDICES!B27,2)</f>
+        <f>ROUND(130*(DADOS_PROJETO!B12/2752.67)/1.1*0.618*INDICES!D27,2)</f>
         <v/>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
-        <is>
-          <t>Índ 1,77m/m² × fator tipol.</t>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>Índ 1,77m/m² × fator tipol (D27)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Elétricas MO</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
@@ -1372,32 +1374,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E5" s="5">
-        <f>ROUND(130*(DADOS_PROJETO!B12/2752.67)/1.1*0.382*INDICES!B27,2)</f>
+        <f>ROUND(130*(DADOS_PROJETO!B12/2752.67)/1.1*0.382*INDICES!D27,2)</f>
         <v/>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
-        <is>
-          <t>Split 38,2% × fator tipol.</t>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Split 38,2% × fator tipol (D27)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Hidro mat.</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>IF BWC/apto</t>
         </is>
@@ -1406,32 +1408,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E6" s="5">
-        <f>ROUND(145*(DADOS_PROJETO!B12/2752.67)/1.1*0.66*IF(VALUE(BRIEFING!B15)&gt;=2,1.15,1),2)</f>
+        <f>ROUND(145*(DADOS_PROJETO!B12/2752.67)/1.1*0.66*INDICES!D35,2)</f>
         <v/>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
-        <is>
-          <t>Índ 1,08m/m² × IF BWC</t>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>Índ 1,08m/m² × fator hidro (D35)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Hidro MO</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
@@ -1440,32 +1442,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E7" s="5">
-        <f>ROUND(145*(DADOS_PROJETO!B12/2752.67)/1.1*0.34*IF(VALUE(BRIEFING!B15)&gt;=2,1.15,1),2)</f>
+        <f>ROUND(145*(DADOS_PROJETO!B12/2752.67)/1.1*0.34*INDICES!D35,2)</f>
         <v/>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
-        <is>
-          <t>Split 34,0% × IF BWC</t>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t>Split 34,0% × fator hidro (D35)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Preventivas</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Mat+MO</t>
         </is>
@@ -1474,7 +1476,7 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -1487,19 +1489,19 @@
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Param.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Gás</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Mat+MO</t>
         </is>
@@ -1508,7 +1510,7 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -1521,19 +1523,19 @@
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Telecom</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Mat+MO</t>
         </is>
@@ -1542,7 +1544,7 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -1555,19 +1557,19 @@
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <f>SUM(F4:F10)</f>
         <v/>
       </c>
@@ -1605,14 +1607,14 @@
           <t>SIST. ESPECIAIS</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F15</f>
         <v/>
       </c>
@@ -1655,12 +1657,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Elevador social</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>N-1 elevadores</t>
         </is>
@@ -1669,354 +1671,354 @@
         <f>MAX(1,DADOS_PROJETO!B9-1)</f>
         <v/>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>192450</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>PU base (5p)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Elevador serv.</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>1un</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>96000</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base (5p)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Gerador</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>IF Gerador+Torres</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
       <c r="E6" s="5">
-        <f>INDICES!B23</f>
+        <f>INDICES!D23</f>
         <v/>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>IF Gerador B11 + Torres B10</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Automação</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>BMS+sensores</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>120000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Piscina</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>IF Piscina B17</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
       <c r="E8" s="5">
-        <f>INDICES!B30</f>
+        <f>INDICES!D30</f>
         <v/>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>IF Piscina (Sim/Não/Aquecida)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>CFTV</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Câmeras+DVR</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>120000</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Pressurização</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>IF Pressurização B9</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
       <c r="E10" s="5">
-        <f>INDICES!B22</f>
+        <f>INDICES!D22</f>
         <v/>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>IF Pressurização</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>SPDA</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Para-raios+malha</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>55000</v>
       </c>
       <c r="F11" s="4">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Interfonia</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Ctrl acesso</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>130000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Bombas</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Recalque+incêndio</t>
         </is>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C13" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>95000</v>
       </c>
       <c r="F13" s="4">
         <f>C13*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Quadros comando</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Bombas+sist</t>
         </is>
       </c>
-      <c r="C14" s="28" t="n">
+      <c r="C14" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>60000</v>
       </c>
       <c r="F14" s="4">
         <f>C14*E14</f>
         <v/>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="22">
         <f>SUM(F4:F14)</f>
         <v/>
       </c>
@@ -2054,14 +2056,14 @@
           <t>CLIMATIZAÇÃO</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F8</f>
         <v/>
       </c>
@@ -2104,12 +2106,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Split</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>1,5/apto</t>
         </is>
@@ -2118,31 +2120,31 @@
         <f>ROUND(DADOS_PROJETO!B6*1.5,0)</f>
         <v/>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>3500</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Param. 1,5/apto</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Exaust.BWC</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>4/pav enclaus.</t>
         </is>
@@ -2151,31 +2153,31 @@
         <f>4*DADOS_PROJETO!B8</f>
         <v/>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>1200</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>4 bwc/pav</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Exaust.churr.</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>2/pav+lazer</t>
         </is>
@@ -2184,31 +2186,31 @@
         <f>2*DADOS_PROJETO!B8+2</f>
         <v/>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>2500</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>2/pav+lazer</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Infra AR</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Dutos+tub</t>
         </is>
@@ -2217,31 +2219,31 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>10</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <f>SUM(F4:F7)</f>
         <v/>
       </c>
@@ -2279,14 +2281,14 @@
           <t>REV. INT. PAREDE</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F15</f>
         <v/>
       </c>
@@ -2329,180 +2331,180 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Reboco</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Massa única</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.35,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.35,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>7</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ 2,85×35%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Chapisco</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Rolado+colante</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.35,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.35,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>5.5</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Cerâm.BWC</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>30×60</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.14,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.14,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E6" s="5">
-        <f>48*INDICES!B20</f>
+        <f>48*INDICES!D20</f>
         <v/>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>PU×fator padrão</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Cerâm.cozinha</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>30×60</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.06,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.06,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E7" s="5">
-        <f>42*INDICES!B20</f>
+        <f>42*INDICES!D20</f>
         <v/>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU×fator padrão</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Porcel.parede</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Comuns</t>
         </is>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.04,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.04,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E8" s="5">
-        <f>85*INDICES!B20</f>
+        <f>85*INDICES!D20</f>
         <v/>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>PU×fator padrão</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Granito bancadas</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Lavat+coz</t>
         </is>
@@ -2511,164 +2513,164 @@
         <f>ROUND(DADOS_PROJETO!B6*3.5,0)</f>
         <v/>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
       <c r="E9" s="5">
-        <f>180*INDICES!B20</f>
+        <f>180*INDICES!D20</f>
         <v/>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>R$ 180×fator padrão</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Arg.colante</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>AC-II/III</t>
         </is>
       </c>
       <c r="C10" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.24,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.24,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>12</v>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Rejunte</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Flexível</t>
         </is>
       </c>
       <c r="C11" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.24,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.24,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="4">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>MO reboco</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C12" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.35,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.35,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>22.5</v>
       </c>
       <c r="F12" s="4">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Split 54,4%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>MO cerâmica</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Assentamento</t>
         </is>
       </c>
       <c r="C13" s="4">
-        <f>ROUND(INDICES!B15*DADOS_PROJETO!B5*0.24,0)</f>
-        <v/>
-      </c>
-      <c r="D13" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D15*DADOS_PROJETO!B5*0.24,0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>35</v>
       </c>
       <c r="F13" s="4">
         <f>C13*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Split 54,4%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>MO granito</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Instalação</t>
         </is>
@@ -2677,31 +2679,31 @@
         <f>ROUND(DADOS_PROJETO!B6*3.5,0)</f>
         <v/>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>35.9</v>
       </c>
       <c r="F14" s="4">
         <f>C14*E14</f>
         <v/>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 36</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="22">
         <f>SUM(F4:F14)</f>
         <v/>
       </c>
@@ -2739,14 +2741,14 @@
           <t>TETO</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F8</f>
         <v/>
       </c>
@@ -2789,144 +2791,144 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Forro ST</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Acartonado</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B16*DADOS_PROJETO!B5*0.70,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D16*DADOS_PROJETO!B5*0.70,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>28</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ 1,16×70%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Forro RU</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>BWC</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B16*DADOS_PROJETO!B5*0.15,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D16*DADOS_PROJETO!B5*0.15,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>35</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Perfis</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Estrutura</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B16*DADOS_PROJETO!B5*0.85,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D16*DADOS_PROJETO!B5*0.85,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>MO forro</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B16*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D16*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>25</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>Split 79,1%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="22">
         <f>SUM(F4:F7)</f>
         <v/>
       </c>
@@ -2964,14 +2966,14 @@
           <t>PISOS</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F11</f>
         <v/>
       </c>
@@ -3014,245 +3016,245 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Contrapiso</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Autonivelante</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>12.1</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ piso×AC (IF shell)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Piso principal</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>IF Tipo Piso</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5*0.50,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5*0.50,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E5" s="5">
-        <f>INDICES!B29</f>
+        <f>INDICES!D29</f>
         <v/>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU IF Tipo Piso × Padrão</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Cimentado</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Garagem 20%</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5*0.20,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5*0.20,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>32</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Granito</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Halls 5%</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5*0.05,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5*0.05,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E7" s="5">
-        <f>180*INDICES!B20</f>
+        <f>180*INDICES!D20</f>
         <v/>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU×fator padrão</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Rodapé</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Poliestireno</t>
         </is>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5*0.35,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5*0.35,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>10.77</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>PU base (10p)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>MO contrapiso</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C9" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>18</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Split 54%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>MO pisos</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Assentamento</t>
         </is>
       </c>
       <c r="C10" s="4">
-        <f>ROUND(INDICES!B14*DADOS_PROJETO!B5*0.70,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D14*DADOS_PROJETO!B5*0.70,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>32</v>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Split 54%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <f>SUM(F4:F10)</f>
         <v/>
       </c>
@@ -3290,14 +3292,14 @@
           <t>PINTURA</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F10</f>
         <v/>
       </c>
@@ -3340,210 +3342,210 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Massa PVA</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Paredes 2dem</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B17*DADOS_PROJETO!B5*0.55,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D17*DADOS_PROJETO!B5*0.55,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>4.29</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ pintura×55%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Acrílica par.</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>3 demãos</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B17*DADOS_PROJETO!B5*0.55,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D17*DADOS_PROJETO!B5*0.55,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>5.4</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base (6p)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Acrílica teto</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>2 demãos</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B17*DADOS_PROJETO!B5*0.20,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D17*DADOS_PROJETO!B5*0.20,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>3.83</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Selador</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B17*DADOS_PROJETO!B5*0.75,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D17*DADOS_PROJETO!B5*0.75,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>2.5</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>MO pintura</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(INDICES!B17*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D17*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>15</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Split 66,2%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>MO lixamento</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Preparação</t>
         </is>
       </c>
       <c r="C9" s="4">
-        <f>ROUND(INDICES!B17*DADOS_PROJETO!B5*0.55,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D17*DADOS_PROJETO!B5*0.55,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Split 66,2%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="inlineStr">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="22">
         <f>SUM(F4:F9)</f>
         <v/>
       </c>
@@ -3581,14 +3583,14 @@
           <t>ESQUADRIAS</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F6</f>
         <v/>
       </c>
@@ -3631,12 +3633,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Esquadrias Al</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Jan+portas</t>
         </is>
@@ -3645,32 +3647,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E4" s="5">
-        <f>280*INDICES!B20*INDICES!B28</f>
+        <f>280*INDICES!D20*INDICES!D28</f>
         <v/>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>R$280 × padrão × entrega</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Serralheria</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>GC+corrimão</t>
         </is>
@@ -3679,32 +3681,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E5" s="5">
-        <f>45*INDICES!B20</f>
+        <f>45*INDICES!D20</f>
         <v/>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>R$45 × fator padrão</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <f>SUM(F4:F5)</f>
         <v/>
       </c>
@@ -3734,7 +3736,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PROJETO — ORÇAMENTO PARAMÉTRICO V2</t>
+          <t>ARTHEN ARBORIS — ORÇAMENTO PARAMÉTRICO V2</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Projeto</t>
+          <t>Arthen Arboris</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3758,11 @@
           <t>Cidade/UF</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Itajaí</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -3815,7 +3821,7 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11">
@@ -3871,14 +3877,14 @@
           <t>LOUÇAS E METAIS</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F5</f>
         <v/>
       </c>
@@ -3921,12 +3927,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Louças+metais</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>IF Tipol+BWC+Padrão+Entrega</t>
         </is>
@@ -3935,32 +3941,32 @@
         <f>DADOS_PROJETO!B6</f>
         <v/>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>apto</t>
         </is>
       </c>
       <c r="E4" s="5">
-        <f>2800*INDICES!B20*INDICES!B26*INDICES!B32*INDICES!B28</f>
+        <f>2800*INDICES!D20*INDICES!D26*INDICES!D32*INDICES!D28</f>
         <v/>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>R$2800 × padrão × tipol × bwc × entrega</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <f>SUM(F4:F4)</f>
         <v/>
       </c>
@@ -3998,14 +4004,14 @@
           <t>FACHADA</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F7</f>
         <v/>
       </c>
@@ -4048,112 +4054,112 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Revestimento</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Conforme briefing</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B18*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D18*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E4" s="5">
-        <f>INDICES!B21</f>
+        <f>INDICES!D21</f>
         <v/>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>IF tipo fachada</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>MO fachada</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Empreitada</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B18*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D18*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>35</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Balancim</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Fachadeiro</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B18*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D18*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>18</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>SUM(F4:F6)</f>
         <v/>
       </c>
@@ -4191,14 +4197,14 @@
           <t>COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F14</f>
         <v/>
       </c>
@@ -4241,198 +4247,198 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Mobiliário</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Áreas comuns</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>540000</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 540k (5p)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Ambientação</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Decoração halls</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
       <c r="E5" s="5">
-        <f>300000*INDICES!B20</f>
+        <f>300000*INDICES!D20</f>
         <v/>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>R$ 300k×fator padrão</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Paisagismo</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr"/>
-      <c r="C6" s="28" t="n">
+      <c r="B6" s="25" t="inlineStr"/>
+      <c r="C6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>120000</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Equip. lazer</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Acad+playground</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>180000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU base (8p)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Limpeza final</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr"/>
+      <c r="B8" s="25" t="inlineStr"/>
       <c r="C8" s="4">
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>12</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 12/m² (10p)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Comunic.visual</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Sinalização</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>47000</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 47k (17p)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Telhado+estrutura</t>
         </is>
@@ -4441,95 +4447,95 @@
         <f>ROUND(DADOS_PROJETO!B5*0.04,0)</f>
         <v/>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>95</v>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Ligações def.</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Água+energia+gás</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>60000</v>
       </c>
       <c r="F11" s="4">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Desmobilização</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Pessoal+equip</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>15000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>PU base (6p)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Paviment.ext.</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Calçadas</t>
         </is>
@@ -4538,31 +4544,31 @@
         <f>ROUND(DADOS_PROJETO!B5*0.06,0)</f>
         <v/>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>80</v>
       </c>
       <c r="F13" s="4">
         <f>C13*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>PU base</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
@@ -4600,14 +4606,14 @@
           <t>IMPREVISTOS</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F5</f>
         <v/>
       </c>
@@ -4650,20 +4656,20 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Imprevistos</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>1,5% do subtotal</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
@@ -4676,19 +4682,19 @@
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Percentual padrão</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <f>SUM(F4:F4)</f>
         <v/>
       </c>
@@ -4714,163 +4720,163 @@
   </cols>
   <sheetData>
     <row r="2">
-      <c r="A2" s="29" t="inlineStr">
-        <is>
-          <t>PARAMÉTRICO V2 — Projeto</t>
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>PARAMÉTRICO V2 — Arthen Arboris</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="30" t="inlineStr">
         <is>
           <t>18/18 macrogrupos bottom-up | 14 dropdowns interativos</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Altere os dropdowns na aba BRIEFING para recalcular automaticamente</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr"/>
+      <c r="A5" s="30" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>FONTES: calibration-indices.json (75 exec + 79 narrativos + IFC + curva ABC)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>PUs: base-pus-cartesian.json (1.504 itens, medianas de 75 executivos)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Splits MO/Material: medianas reais de 38 executivos detalhados</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr"/>
+      <c r="A9" s="30" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>14 DROPDOWNS ATIVOS:</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. Laje: Convencional/Protendida/Nervurada → concreto, aço, forma, escoramento</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. Subsolos: 0-3 → contenção, mov.terra, impermeabilização, fundação</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. Fundação: Hélice/Tubulão/Sapata → infraestrutura</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. Padrão: Médio/Médio-Alto/Alto/Luxo → acabamentos, esquadrias, louças (×0.85-1.35)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  5. Fachada: Textura/Cerâmica/Pele de vidro/ACM → PU fachada R$ 100-350/m²</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  6. Pressurização: Sim/Não → +R$ 80k</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  7. Torres: 1/2/3 → gerador proporcional</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  8. Gerador dedicado: Sim/Não → R$ 0-350k</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  9. Entrega: Completa/Shell → Shell desconta ~15% (pisos, pintura, rev, louças, esq)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  10. Tipologia: Studios/1-2D/3-4D/Misto → pontos elétricos, louças (×0.65-1.20)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  11. Pé-Direito: Baixo/Padrão/Alto/Duplo → estrutura (×0.97-1.12), fachada</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  12. BWC/apto: 1-4 → hidro, louças (×1.0-1.80), rev.parede, impermeab</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  13. Tipo Piso: Porcelanato/Laminado/Misto → PU pisos R$ 65-81/m²</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">  14. Piscina: Sim/Não/Aquecida → R$ 0/220k/320k</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr"/>
+      <c r="A25" s="30" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>Baseado revisão Patricia (coord. custos) + calibração 75 exec — 24/mar/2026</t>
         </is>
@@ -4954,7 +4960,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -5005,7 +5011,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Textura</t>
+          <t>Cerâmica</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -5090,7 +5096,7 @@
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>3-4 Dormitórios</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -5141,7 +5147,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Misto</t>
+          <t>Porcelanato</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -5226,27 +5232,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>ÍNDICES CALIBRADOS — REAGEM AO BRIEFING</t>
+          <t>ÍNDICES CALIBRADOS — HÍBRIDO: BRIEFING + OVERRIDE MANUAL</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="inlineStr">
         <is>
-          <t>NÃO EDITAR — valores calculados automaticamente</t>
+          <t>B=calculado via BRIEFING (não editar) | C=override manual (edite para sobrescrever) | D=valor efetivo usado nas abas de macrogrupo (= Override se preenchido, senão B)</t>
         </is>
       </c>
     </row>
@@ -5258,22 +5265,27 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Valor calc</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
+          <t>Override</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Efetivo</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
           <t>Unidade</t>
         </is>
       </c>
-      <c r="D4" s="12" t="inlineStr">
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Fonte</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Fórmula</t>
         </is>
       </c>
     </row>
@@ -5287,19 +5299,19 @@
         <f>IF(BRIEFING!B4="Protendida",0.22,IF(BRIEFING!B4="Nervurada",0.20,0.25))</f>
         <v/>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="17">
+        <f>IF(C5="",B5,C5)</f>
+        <v/>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>m³/m²</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>Master 7p exec</t>
-        </is>
-      </c>
-      <c r="E5" s="17" t="inlineStr">
-        <is>
-          <t>IF Laje</t>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>Master 7p exec | IF Laje</t>
         </is>
       </c>
     </row>
@@ -5313,19 +5325,19 @@
         <f>IF(BRIEFING!B4="Protendida",70,IF(BRIEFING!B4="Nervurada",90,106))</f>
         <v/>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="17">
+        <f>IF(C6="",B6,C6)</f>
+        <v/>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>kg/m³</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>Master 7p+11p narr</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>IF Laje</t>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Master 7p+11p narr | IF Laje</t>
         </is>
       </c>
     </row>
@@ -5339,19 +5351,19 @@
         <f>IF(BRIEFING!B4="Protendida",8,0)</f>
         <v/>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="17">
+        <f>IF(C7="",B7,C7)</f>
+        <v/>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>kg/m²</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Master protendida</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>IF Laje=Protendida</t>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>Master protendida | IF Laje=Protendida</t>
         </is>
       </c>
     </row>
@@ -5365,19 +5377,19 @@
         <f>IF(BRIEFING!B4="Protendida",6.05,IF(BRIEFING!B4="Nervurada",6.5,7.12))</f>
         <v/>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="17">
+        <f>IF(C8="",B8,C8)</f>
+        <v/>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>m²/m³</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Master 7p exec</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>IF Laje</t>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>Master 7p exec | IF Laje</t>
         </is>
       </c>
     </row>
@@ -5391,19 +5403,19 @@
         <f>IF(BRIEFING!B4="Protendida",50,IF(BRIEFING!B4="Nervurada",35,0))</f>
         <v/>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="10" t="n"/>
+      <c r="D9" s="18">
+        <f>IF(C9="",B9,C9)</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>R$/m²</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>PU base 7p</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>IF Laje</t>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>PU base 7p | IF Laje</t>
         </is>
       </c>
     </row>
@@ -5417,13 +5429,17 @@
         <f>IF(BRIEFING!B4="Protendida",40,30)</f>
         <v/>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="17">
+        <f>IF(C10="",B10,C10)</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>MPa</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>IF Laje</t>
         </is>
@@ -5439,19 +5455,19 @@
         <f>ROUND(DADOS_PROJETO!B5/75,0)*(1+VALUE(BRIEFING!B5)*0.15)</f>
         <v/>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="17">
+        <f>IF(C11="",B11,C11)</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>~1 est/75m² + sub</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>AC/75 × (1+sub×15%)</t>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>~1 est/75m² + sub | AC/75 × (1+sub×15%)</t>
         </is>
       </c>
     </row>
@@ -5465,19 +5481,19 @@
         <f>IF(BRIEFING!B6="Hélice",18,IF(BRIEFING!B6="Tubulão",12,0))+VALUE(BRIEFING!B5)*2</f>
         <v/>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="17">
+        <f>IF(C12="",B12,C12)</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Tipo + prof.sub</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>IF Fundação + sub×2m</t>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>Tipo + prof.sub | IF Fundação + sub×2m</t>
         </is>
       </c>
     </row>
@@ -5491,19 +5507,19 @@
         <f>2.25*IF(BRIEFING!B12="Shell",0.75,1)*IF(BRIEFING!B14="Duplo",1.15,IF(BRIEFING!B14="Alto (3.20)",1.05,1))</f>
         <v/>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="17">
+        <f>IF(C13="",B13,C13)</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>2,25 × shell × pé-dir</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>IF Entrega + Pé-Direito</t>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>2,25 × shell × pé-dir | IF Entrega + Pé-Direito</t>
         </is>
       </c>
     </row>
@@ -5517,19 +5533,19 @@
         <f>1.70*IF(BRIEFING!B12="Shell",0.40,1)</f>
         <v/>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="17">
+        <f>IF(C14="",B14,C14)</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>1,70 × shell</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>IF Entrega (shell = 40%)</t>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>1,70 × shell | IF Entrega (shell = 40%)</t>
         </is>
       </c>
     </row>
@@ -5543,19 +5559,19 @@
         <f>2.85*IF(BRIEFING!B12="Shell",0.50,1)*IF(VALUE(BRIEFING!B15)&gt;=2,1.15,IF(VALUE(BRIEFING!B15)&gt;=1,1.0,0.85))</f>
         <v/>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="17">
+        <f>IF(C15="",B15,C15)</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>2,85 × shell × bwc</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>IF Entrega + BWC/apto</t>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>2,85 × shell × bwc | IF Entrega + BWC/apto</t>
         </is>
       </c>
     </row>
@@ -5569,19 +5585,19 @@
         <f>1.16*IF(BRIEFING!B12="Shell",0.45,1)</f>
         <v/>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="17">
+        <f>IF(C16="",B16,C16)</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>1,16 × shell</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>IF Entrega (shell = 45%)</t>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>1,16 × shell | IF Entrega (shell = 45%)</t>
         </is>
       </c>
     </row>
@@ -5595,19 +5611,19 @@
         <f>5.65*IF(BRIEFING!B12="Shell",0.40,1)</f>
         <v/>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="17">
+        <f>IF(C17="",B17,C17)</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>5,65 × shell</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>IF Entrega (shell = 40%)</t>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>5,65 × shell | IF Entrega (shell = 40%)</t>
         </is>
       </c>
     </row>
@@ -5621,19 +5637,19 @@
         <f>IF(BRIEFING!B8="Pele de vidro",1.8,IF(BRIEFING!B8="ACM",1.7,1.55))*IF(BRIEFING!B14="Duplo",1.12,IF(BRIEFING!B14="Alto (3.20)",1.05,1))</f>
         <v/>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="17">
+        <f>IF(C18="",B18,C18)</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Tipo fachada × pé-dir</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>IF Fachada + Pé-Direito</t>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>Tipo fachada × pé-dir | IF Fachada + Pé-Direito</t>
         </is>
       </c>
     </row>
@@ -5647,19 +5663,19 @@
         <f>0.37+VALUE(BRIEFING!B5)*0.05+IF(VALUE(BRIEFING!B15)&gt;=3,0.04,IF(VALUE(BRIEFING!B15)&gt;=2,0.03,0))</f>
         <v/>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="17">
+        <f>IF(C19="",B19,C19)</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>m²/m²</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Base + sub + bwc</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>IF Sub + BWC</t>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>Base + sub + bwc | IF Sub + BWC</t>
         </is>
       </c>
     </row>
@@ -5673,13 +5689,17 @@
         <f>IF(BRIEFING!B7="Luxo",1.35,IF(BRIEFING!B7="Alto",1.15,IF(BRIEFING!B7="Médio-Alto",1.0,0.85)))</f>
         <v/>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="17">
+        <f>IF(C20="",B20,C20)</f>
+        <v/>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>fator</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr">
+      <c r="F20" s="14" t="inlineStr">
         <is>
           <t>IF Padrão</t>
         </is>
@@ -5695,19 +5715,19 @@
         <f>IF(BRIEFING!B8="Pele de vidro",350,IF(BRIEFING!B8="ACM",280,IF(BRIEFING!B8="Cerâmica",180,100)))</f>
         <v/>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="18">
+        <f>IF(C21="",B21,C21)</f>
+        <v/>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>R$/m²</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>PU base + briefing</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>IF Fachada tipo</t>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>PU base + briefing | IF Fachada tipo</t>
         </is>
       </c>
     </row>
@@ -5721,19 +5741,19 @@
         <f>IF(BRIEFING!B9="Sim",80000,0)</f>
         <v/>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="18">
+        <f>IF(C22="",B22,C22)</f>
+        <v/>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>Param. base</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>IF Sim</t>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>Param. base | IF Sim</t>
         </is>
       </c>
     </row>
@@ -5747,19 +5767,19 @@
         <f>IF(BRIEFING!B11="Não",0,IF(BRIEFING!B10="3",350000,IF(BRIEFING!B10="2",250000,180000)))</f>
         <v/>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="18">
+        <f>IF(C23="",B23,C23)</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>IF Gerador Sim + Torres</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>IF Gerador + Torres</t>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>IF Gerador Sim + Torres | IF Gerador + Torres</t>
         </is>
       </c>
     </row>
@@ -5773,19 +5793,19 @@
         <f>IF(VALUE(BRIEFING!B5)&gt;0,VALUE(BRIEFING!B5)*3.5*120*350,0)</f>
         <v/>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="18">
+        <f>IF(C24="",B24,C24)</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Sub×prof×perim×R$</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>IF Sub&gt;0</t>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>Sub×prof×perim×R$ | IF Sub&gt;0</t>
         </is>
       </c>
     </row>
@@ -5799,19 +5819,19 @@
         <f>IF(VALUE(BRIEFING!B5)&gt;0,17+VALUE(BRIEFING!B5)*15,17)</f>
         <v/>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="18">
+        <f>IF(C25="",B25,C25)</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>R$/m²</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Base + sub×15</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>IF Sub&gt;0</t>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>Base + sub×15 | IF Sub&gt;0</t>
         </is>
       </c>
     </row>
@@ -5825,19 +5845,19 @@
         <f>IF(BRIEFING!B13="Studios",0.65,IF(BRIEFING!B13="1-2 Dormitórios",0.85,IF(BRIEFING!B13="3-4 Dormitórios",1.20,1.0)))</f>
         <v/>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="17">
+        <f>IF(C26="",B26,C26)</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>fator</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>Studios menos louças</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>IF Tipologia</t>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>Studios menos louças | IF Tipologia</t>
         </is>
       </c>
     </row>
@@ -5851,19 +5871,19 @@
         <f>IF(BRIEFING!B13="Studios",0.80,IF(BRIEFING!B13="3-4 Dormitórios",1.15,1.0))</f>
         <v/>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="17">
+        <f>IF(C27="",B27,C27)</f>
+        <v/>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>fator</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Studios menos pontos</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>IF Tipologia</t>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>Studios menos pontos | IF Tipologia</t>
         </is>
       </c>
     </row>
@@ -5877,19 +5897,19 @@
         <f>IF(BRIEFING!B12="Shell",0.85,1.0)</f>
         <v/>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="17">
+        <f>IF(C28="",B28,C28)</f>
+        <v/>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>fator</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Shell desconta ~15% total</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>IF Entrega</t>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>Shell desconta ~15% total | IF Entrega</t>
         </is>
       </c>
     </row>
@@ -5900,22 +5920,22 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>IF(BRIEFING!B16="Porcelanato",81.21,IF(BRIEFING!B16="Laminado",65,73))*INDICES!B20</f>
-        <v/>
-      </c>
-      <c r="C29" t="inlineStr">
+        <f>IF(BRIEFING!B16="Porcelanato",81.21,IF(BRIEFING!B16="Laminado",65,73))*INDICES!D20</f>
+        <v/>
+      </c>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="18">
+        <f>IF(C29="",B29,C29)</f>
+        <v/>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>R$/m²</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Tipo piso × padrão</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>IF Tipo Piso × Padrão</t>
+      <c r="F29" s="14" t="inlineStr">
+        <is>
+          <t>Tipo piso × padrão | IF Tipo Piso × Padrão (usa D20=efetivo)</t>
         </is>
       </c>
     </row>
@@ -5929,19 +5949,19 @@
         <f>IF(BRIEFING!B17="Aquecida",320000,IF(BRIEFING!B17="Sim",220000,0))</f>
         <v/>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="18">
+        <f>IF(C30="",B30,C30)</f>
+        <v/>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>R$</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>Param. base</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>IF Piscina</t>
+      <c r="F30" s="14" t="inlineStr">
+        <is>
+          <t>Param. base | IF Piscina</t>
         </is>
       </c>
     </row>
@@ -5955,19 +5975,19 @@
         <f>IF(BRIEFING!B14="Duplo",1.12,IF(BRIEFING!B14="Alto (3.20)",1.05,IF(BRIEFING!B14="Baixo (2.80)",0.97,1.0)))</f>
         <v/>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="17">
+        <f>IF(C31="",B31,C31)</f>
+        <v/>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>fator</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
-        <is>
-          <t>Pé-dir afeta estrutura</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>IF Pé-Direito</t>
+      <c r="F31" s="14" t="inlineStr">
+        <is>
+          <t>Pé-dir afeta estrutura | IF Pé-Direito</t>
         </is>
       </c>
     </row>
@@ -5981,25 +6001,104 @@
         <f>IF(VALUE(BRIEFING!B15)&gt;=4,1.80,IF(VALUE(BRIEFING!B15)&gt;=3,1.50,IF(VALUE(BRIEFING!B15)&gt;=2,1.20,1.0)))</f>
         <v/>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="17">
+        <f>IF(C32="",B32,C32)</f>
+        <v/>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>fator</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Mais bwc = mais louças</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>IF BWC/apto</t>
+      <c r="F32" s="14" t="inlineStr">
+        <is>
+          <t>Mais bwc = mais louças | IF BWC/apto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Fator viga protendida</t>
+        </is>
+      </c>
+      <c r="B33" s="5">
+        <f>IF(BRIEFING!B4="Protendida",0.08,0.30)</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="17">
+        <f>IF(C33="",B33,C33)</f>
+        <v/>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>fator</t>
+        </is>
+      </c>
+      <c r="F33" s="14" t="inlineStr">
+        <is>
+          <t>Peso viga/m² conforme laje | IF Laje (0.08 prot / 0.30 conv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Fator laje protendida</t>
+        </is>
+      </c>
+      <c r="B34" s="5">
+        <f>IF(BRIEFING!B4="Protendida",0.60,0.35)</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="17">
+        <f>IF(C34="",B34,C34)</f>
+        <v/>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>fator</t>
+        </is>
+      </c>
+      <c r="F34" s="14" t="inlineStr">
+        <is>
+          <t>Peso laje/m² conforme tipo | IF Laje (0.60 prot / 0.35 conv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Fator hidro BWC</t>
+        </is>
+      </c>
+      <c r="B35" s="5">
+        <f>IF(VALUE(BRIEFING!B15)&gt;=2,1.15,1)</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="17">
+        <f>IF(C35="",B35,C35)</f>
+        <v/>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>fator</t>
+        </is>
+      </c>
+      <c r="F35" s="14" t="inlineStr">
+        <is>
+          <t>Mais bwc = mais hidro | IF BWC&gt;=2 (1.15 / 1.0)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6066,7 +6165,7 @@
         <f>D4/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C4" s="18">
+      <c r="C4" s="19">
         <f>D4/D22</f>
         <v/>
       </c>
@@ -6090,7 +6189,7 @@
         <f>D5/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="19">
         <f>D5/D22</f>
         <v/>
       </c>
@@ -6114,7 +6213,7 @@
         <f>D6/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="19">
         <f>D6/D22</f>
         <v/>
       </c>
@@ -6138,7 +6237,7 @@
         <f>D7/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>D7/D22</f>
         <v/>
       </c>
@@ -6162,7 +6261,7 @@
         <f>D8/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="19">
         <f>D8/D22</f>
         <v/>
       </c>
@@ -6186,7 +6285,7 @@
         <f>D9/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>D9/D22</f>
         <v/>
       </c>
@@ -6210,7 +6309,7 @@
         <f>D10/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="19">
         <f>D10/D22</f>
         <v/>
       </c>
@@ -6234,7 +6333,7 @@
         <f>D11/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="19">
         <f>D11/D22</f>
         <v/>
       </c>
@@ -6258,7 +6357,7 @@
         <f>D12/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="19">
         <f>D12/D22</f>
         <v/>
       </c>
@@ -6282,7 +6381,7 @@
         <f>D13/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="19">
         <f>D13/D22</f>
         <v/>
       </c>
@@ -6306,7 +6405,7 @@
         <f>D14/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="19">
         <f>D14/D22</f>
         <v/>
       </c>
@@ -6330,7 +6429,7 @@
         <f>D15/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="19">
         <f>D15/D22</f>
         <v/>
       </c>
@@ -6354,7 +6453,7 @@
         <f>D16/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="19">
         <f>D16/D22</f>
         <v/>
       </c>
@@ -6378,7 +6477,7 @@
         <f>D17/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="19">
         <f>D17/D22</f>
         <v/>
       </c>
@@ -6402,7 +6501,7 @@
         <f>D18/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="19">
         <f>D18/D22</f>
         <v/>
       </c>
@@ -6426,7 +6525,7 @@
         <f>D19/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="19">
         <f>D19/D22</f>
         <v/>
       </c>
@@ -6450,7 +6549,7 @@
         <f>D20/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>D20/D22</f>
         <v/>
       </c>
@@ -6474,7 +6573,7 @@
         <f>D21/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <f>D21/D22</f>
         <v/>
       </c>
@@ -6489,16 +6588,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="20">
+      <c r="B22" s="21">
         <f>D22/DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <f>SUM(D4:D21)</f>
         <v/>
       </c>
@@ -6536,14 +6635,14 @@
           <t>SUPRAESTRUTURA</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F14</f>
         <v/>
       </c>
@@ -6586,277 +6685,277 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Concreto Pilares</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>fck30</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B5*DADOS_PROJETO!B5*0.22*INDICES!B31,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D5*DADOS_PROJETO!B5*0.22*INDICES!D31,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>590</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Índ×AC×22% × pé-dir (7p)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Concreto Vigas</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>fck30</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B5*DADOS_PROJETO!B5*IF(BRIEFING!B4="Protendida",0.08,0.30),0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D5*DADOS_PROJETO!B5*INDICES!D33,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>590</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
-        <is>
-          <t>IF Laje→peso vigas</t>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Índ conc × AC × fator viga (D33)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Concreto Lajes</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>fck conforme laje</t>
         </is>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(INDICES!B5*DADOS_PROJETO!B5*IF(BRIEFING!B4="Protendida",0.60,0.35),0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D5*DADOS_PROJETO!B5*INDICES!D34,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
       <c r="E6" s="5">
-        <f>IF(INDICES!B10=40,690,590)</f>
+        <f>IF(INDICES!D10=40,690,590)</f>
         <v/>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
-        <is>
-          <t>IF fck→PU</t>
+      <c r="G6" s="27" t="inlineStr">
+        <is>
+          <t>Índ conc × AC × fator laje (D34)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Concreto Escadas</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>fck30</t>
         </is>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(INDICES!B5*DADOS_PROJETO!B5*0.05,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D5*DADOS_PROJETO!B5*0.05,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>590</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>Índ×AC×5%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Concreto Blocos</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Baldrame fck30</t>
         </is>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(INDICES!B5*DADOS_PROJETO!B5*0.05,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D5*DADOS_PROJETO!B5*0.05,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>590</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Índ×AC×5%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Aço CA-50</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Convencional</t>
         </is>
       </c>
       <c r="C9" s="4">
-        <f>ROUND(INDICES!B6*INDICES!B5*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D6*INDICES!D5*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>8.67</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Índ aço×conc×AC</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Cordoalha CP-190</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Protensão</t>
         </is>
       </c>
       <c r="C10" s="4">
-        <f>ROUND(INDICES!B7*DADOS_PROJETO!B5*0.65,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D7*DADOS_PROJETO!B5*0.65,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>22</v>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>IF Prot→8kg/m² laje</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Forma</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Compensado plastif.</t>
         </is>
       </c>
       <c r="C11" s="4">
-        <f>ROUND(INDICES!B8*INDICES!B5*DADOS_PROJETO!B5,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D8*INDICES!D5*DADOS_PROJETO!B5,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>88.06999999999999</v>
       </c>
       <c r="F11" s="4">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Índ forma×conc×AC</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Escoramento</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Metálico</t>
         </is>
@@ -6865,32 +6964,32 @@
         <f>ROUND(DADOS_PROJETO!B5*0.65,0)</f>
         <v/>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E12" s="5">
-        <f>INDICES!B9</f>
+        <f>INDICES!D9</f>
         <v/>
       </c>
       <c r="F12" s="4">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>IF Laje→PU escor</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>MO Estrutura</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>Empreitada (32,6%)</t>
         </is>
@@ -6899,7 +6998,7 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
@@ -6912,19 +7011,19 @@
         <f>C13*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Split 32,6% MO (10p)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F14" s="21">
+      <c r="F14" s="22">
         <f>SUM(F4:F13)</f>
         <v/>
       </c>
@@ -6962,14 +7061,14 @@
           <t>INFRAESTRUTURA</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F13</f>
         <v/>
       </c>
@@ -7012,78 +7111,78 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Perfuração hélice</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Ø40cm</t>
         </is>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(INDICES!B11*INDICES!B12,0)</f>
-        <v/>
-      </c>
-      <c r="D4" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D11*INDICES!D12,0)</f>
+        <v/>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>82</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 82/m (6p)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Concreto estacas</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>fck30</t>
         </is>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(INDICES!B11*3.14159*0.04*INDICES!B12,0)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
+        <f>ROUND(INDICES!D11*3.14159*0.04*INDICES!D12,0)</f>
+        <v/>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>632</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 632 (6p)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Concreto blocos</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Baldrames</t>
         </is>
@@ -7092,31 +7191,31 @@
         <f>ROUND(0.02*DADOS_PROJETO!B5,0)</f>
         <v/>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>m³</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>590</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Índ 0,02 m³/m²</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Aço CA-50</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
@@ -7125,31 +7224,31 @@
         <f>ROUND(90*(C5+C6),0)</f>
         <v/>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>8.77</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 8,77 (7p)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Forma</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Blocos/baldrames</t>
         </is>
@@ -7158,104 +7257,104 @@
         <f>ROUND(0.10*DADOS_PROJETO!B5,0)</f>
         <v/>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>45.64</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 45,64 (8p)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Arrasamento</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Estacas</t>
         </is>
       </c>
       <c r="C9" s="4">
-        <f>INDICES!B11</f>
-        <v/>
-      </c>
-      <c r="D9" s="24" t="inlineStr">
+        <f>INDICES!D11</f>
+        <v/>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>65</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 65 (2p)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Limpeza/remoção</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Solo perfuração</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>35000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 35k (2p)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>MO fundação</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>Empreitada (35,5%)</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
@@ -7268,52 +7367,52 @@
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Split 35,5% (7p)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Contenção</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>Se houver subsolo</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n">
+      <c r="C12" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
       <c r="E12" s="5">
-        <f>INDICES!B24</f>
+        <f>INDICES!D24</f>
         <v/>
       </c>
       <c r="F12" s="4">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>IF Sub&gt;0</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="22">
         <f>SUM(F4:F12)</f>
         <v/>
       </c>
@@ -7351,14 +7450,14 @@
           <t>MOV. TERRA</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F5</f>
         <v/>
       </c>
@@ -7401,12 +7500,12 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Corte+aterro+bota-fora</t>
         </is>
@@ -7415,32 +7514,32 @@
         <f>DADOS_PROJETO!B5</f>
         <v/>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
       <c r="E4" s="5">
-        <f>INDICES!B25</f>
+        <f>INDICES!D25</f>
         <v/>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Param. base + IF sub</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="22">
         <f>SUM(F4:F4)</f>
         <v/>
       </c>
@@ -7478,14 +7577,14 @@
           <t>GERENCIAMENTO</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="G1" s="23" t="inlineStr">
         <is>
           <t>Total:</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="G2" s="23">
+      <c r="G2" s="24">
         <f>F24</f>
         <v/>
       </c>
@@ -7528,140 +7627,140 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Projetos</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Arq+compl+compat</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="24" t="inlineStr">
+      <c r="D4" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>650000</v>
       </c>
       <c r="F4" s="4">
         <f>C4*E4</f>
         <v/>
       </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="G4" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>Consultorias</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>ATP+compat BIM</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>180000</v>
       </c>
       <c r="F5" s="4">
         <f>C5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Ensaios</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Ctrl tecnol.</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="24" t="inlineStr">
+      <c r="D6" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>130000</v>
       </c>
       <c r="F6" s="4">
         <f>C6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Taxas e seguros</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Incorp+licenças</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>380000</v>
       </c>
       <c r="F7" s="4">
         <f>C7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="26" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Engenheiro PJ</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>1×prazo</t>
         </is>
@@ -7670,31 +7769,31 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>10500</v>
       </c>
       <c r="F8" s="4">
         <f>C8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t>Master R$ 10,5k (5p)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>Mestre obras</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>1×prazo</t>
         </is>
@@ -7703,31 +7802,31 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D9" s="24" t="inlineStr">
+      <c r="D9" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>9940</v>
       </c>
       <c r="F9" s="4">
         <f>C9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="26" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Master R$ 9,9k (4p)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Encarregado</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>1×prazo</t>
         </is>
@@ -7736,31 +7835,31 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D10" s="24" t="inlineStr">
+      <c r="D10" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>8000</v>
       </c>
       <c r="F10" s="4">
         <f>C10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Narrativo R$ 8k</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>Estagiário</t>
         </is>
       </c>
-      <c r="B11" s="24" t="inlineStr">
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>2×prazo</t>
         </is>
@@ -7769,31 +7868,31 @@
         <f>DADOS_PROJETO!B11*2</f>
         <v/>
       </c>
-      <c r="D11" s="24" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>1580</v>
       </c>
       <c r="F11" s="4">
         <f>C11*E11</f>
         <v/>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Master R$ 1,6k (3p)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Téc.segurança</t>
         </is>
       </c>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>1×prazo</t>
         </is>
@@ -7802,31 +7901,31 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D12" s="24" t="inlineStr">
+      <c r="D12" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>6000</v>
       </c>
       <c r="F12" s="4">
         <f>C12*E12</f>
         <v/>
       </c>
-      <c r="G12" s="26" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>PJ R$ 6k/mês</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>Almoxarife</t>
         </is>
       </c>
-      <c r="B13" s="24" t="inlineStr">
+      <c r="B13" s="25" t="inlineStr">
         <is>
           <t>1×prazo</t>
         </is>
@@ -7835,31 +7934,31 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D13" s="24" t="inlineStr">
+      <c r="D13" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>3377</v>
       </c>
       <c r="F13" s="4">
         <f>C13*E13</f>
         <v/>
       </c>
-      <c r="G13" s="26" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Master R$ 3,4k (4p)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Limpeza obra</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>2×prazo</t>
         </is>
@@ -7868,31 +7967,31 @@
         <f>DADOS_PROJETO!B11*2</f>
         <v/>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>2500</v>
       </c>
       <c r="F14" s="4">
         <f>C14*E14</f>
         <v/>
       </c>
-      <c r="G14" s="26" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>PJ R$ 2,5k/mês</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Vigilância</t>
         </is>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
         <is>
           <t>1×prazo</t>
         </is>
@@ -7901,39 +8000,39 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="26" t="n">
         <v>15261</v>
       </c>
       <c r="F15" s="4">
         <f>C15*E15</f>
         <v/>
       </c>
-      <c r="G15" s="26" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>Narrativo R$ 15,3k</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>EPCs</t>
         </is>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>Fixo por porte</t>
         </is>
       </c>
-      <c r="C16" s="28" t="n">
+      <c r="C16" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
@@ -7946,19 +8045,19 @@
         <f>C16*E16</f>
         <v/>
       </c>
-      <c r="G16" s="26" t="inlineStr">
+      <c r="G16" s="27" t="inlineStr">
         <is>
           <t>Master 75 exec</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>EPI</t>
         </is>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="25" t="inlineStr">
         <is>
           <t>Individual</t>
         </is>
@@ -7967,127 +8066,127 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <v>908</v>
       </c>
       <c r="F17" s="4">
         <f>C17*E17</f>
         <v/>
       </c>
-      <c r="G17" s="26" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 908 (8p)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Meio ambiente</t>
         </is>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>PCMAT+PCMSO</t>
         </is>
       </c>
-      <c r="C18" s="28" t="n">
+      <c r="C18" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>45000</v>
       </c>
       <c r="F18" s="4">
         <f>C18*E18</f>
         <v/>
       </c>
-      <c r="G18" s="26" t="inlineStr">
+      <c r="G18" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Op. inicial</t>
         </is>
       </c>
-      <c r="B19" s="24" t="inlineStr">
+      <c r="B19" s="25" t="inlineStr">
         <is>
           <t>Mobilização</t>
         </is>
       </c>
-      <c r="C19" s="28" t="n">
+      <c r="C19" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>55000</v>
       </c>
       <c r="F19" s="4">
         <f>C19*E19</f>
         <v/>
       </c>
-      <c r="G19" s="26" t="inlineStr">
+      <c r="G19" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Inst. provisórias</t>
         </is>
       </c>
-      <c r="B20" s="24" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>Canteiro+containers</t>
         </is>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C20" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="24" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>160000</v>
       </c>
       <c r="F20" s="4">
         <f>C20*E20</f>
         <v/>
       </c>
-      <c r="G20" s="26" t="inlineStr">
+      <c r="G20" s="27" t="inlineStr">
         <is>
           <t>Param. base</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Desp. consumo</t>
         </is>
       </c>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>Água+en+internet+IPTU</t>
         </is>
@@ -8096,95 +8195,95 @@
         <f>DADOS_PROJETO!B11</f>
         <v/>
       </c>
-      <c r="D21" s="24" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>mês</t>
         </is>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="26" t="n">
         <v>11500</v>
       </c>
       <c r="F21" s="4">
         <f>C21*E21</f>
         <v/>
       </c>
-      <c r="G21" s="26" t="inlineStr">
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>PU base (9p)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Equipamentos</t>
         </is>
       </c>
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>Grua+cremalheira</t>
         </is>
       </c>
-      <c r="C22" s="28" t="n">
+      <c r="C22" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="24" t="inlineStr">
+      <c r="D22" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="26" t="n">
         <v>480000</v>
       </c>
       <c r="F22" s="4">
         <f>C22*E22</f>
         <v/>
       </c>
-      <c r="G22" s="26" t="inlineStr">
+      <c r="G22" s="27" t="inlineStr">
         <is>
           <t>Narrativo</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Comunic.visual</t>
         </is>
       </c>
-      <c r="B23" s="24" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Placas+tapume</t>
         </is>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C23" s="29" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="24" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="26" t="n">
         <v>47000</v>
       </c>
       <c r="F23" s="4">
         <f>C23*E23</f>
         <v/>
       </c>
-      <c r="G23" s="26" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>PU base R$ 47k (17p)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="inlineStr">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F24" s="21">
+      <c r="F24" s="22">
         <f>SUM(F4:F23)</f>
         <v/>
       </c>
